--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104701_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104701_W27.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.416</v>
+        <v>6.3573</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6896</v>
+        <v>6.7817</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2735</v>
+        <v>-0.4244</v>
       </c>
       <c r="G2" t="n">
-        <v>1.215</v>
+        <v>1.2171</v>
       </c>
       <c r="H2" t="n">
-        <v>0.306</v>
+        <v>0.2991</v>
       </c>
       <c r="I2" t="n">
-        <v>0.909</v>
+        <v>0.918</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4584</v>
+        <v>2.4349</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7867</v>
+        <v>1.7647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2434</v>
+        <v>-1.2179</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.4807</v>
+        <v>-1.4656</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0403</v>
+        <v>0.9824000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2461</v>
+        <v>0.3758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7942</v>
+        <v>0.6066</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="W2" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.598</v>
+        <v>1.0067</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5425</v>
+        <v>1.7821</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9446</v>
+        <v>-0.7753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9267</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3203</v>
+        <v>1.3184</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3945</v>
+        <v>-0.3916</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4053</v>
+        <v>1.3989</v>
       </c>
       <c r="K3" t="n">
-        <v>1.368</v>
+        <v>1.3617</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4795</v>
+        <v>-0.4722</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3111</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>1.364</v>
+        <v>0.6108</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9618</v>
+        <v>0.9321</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2356</v>
+        <v>0.9236</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2738</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.325</v>
+        <v>-0.4963</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1891</v>
+        <v>-0.477</v>
       </c>
       <c r="I4" t="n">
-        <v>0.136</v>
+        <v>-0.0193</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6363</v>
+        <v>0.1062</v>
       </c>
       <c r="K4" t="n">
-        <v>0.599</v>
+        <v>0.0689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3113</v>
+        <v>-0.6025</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4099</v>
+        <v>-0.546</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09859999999999999</v>
+        <v>-0.0565</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2492</v>
+        <v>1.2008</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4386</v>
+        <v>0.8174</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1893</v>
+        <v>0.3834</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8716</v>
+        <v>0.9129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6843</v>
+        <v>0.9885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1873</v>
+        <v>-0.0756</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5033</v>
+        <v>0.3255</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.482</v>
+        <v>0.1868</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0213</v>
+        <v>0.1387</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1066</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0693</v>
+        <v>0.5893</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6099</v>
+        <v>-0.3011</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5513</v>
+        <v>-0.4025</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0586</v>
+        <v>0.1014</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1481</v>
+        <v>0.202</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5777</v>
+        <v>0.2042</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5704</v>
+        <v>-0.0022</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.6663</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3668</v>
+        <v>-0.6797</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6012</v>
+        <v>1.346</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2491</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.521</v>
+        <v>-1.0314</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2719</v>
+        <v>0.4109</v>
       </c>
       <c r="J6" t="n">
-        <v>1.773</v>
+        <v>-0.2196</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3409</v>
+        <v>-0.4277</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5679</v>
+        <v>0.2081</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5239</v>
+        <v>-0.4009</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8198</v>
+        <v>-0.6037</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2959</v>
+        <v>0.2028</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.722</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.6922</v>
+        <v>-0.079</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8771</v>
+        <v>-0.4601</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8151</v>
+        <v>0.3812</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6595</v>
+        <v>0.6579</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5989</v>
+        <v>1.3813</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2584</v>
+        <v>-0.7233000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.9435</v>
+        <v>1.2339</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8701</v>
+        <v>1.5112</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0734</v>
+        <v>-0.2773</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.5818</v>
+        <v>1.7347</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5857</v>
+        <v>2.3162</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.9962</v>
+        <v>-0.5816</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3617</v>
+        <v>-0.5007</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2844</v>
+        <v>-0.805</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0772</v>
+        <v>0.3043</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-3.6421</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0152</v>
+        <v>1.6108</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6635</v>
+        <v>0.952</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3517</v>
+        <v>0.6589</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>2.3367</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3551</v>
+        <v>-0.2338</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9694</v>
+        <v>-2.4256</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3245</v>
+        <v>2.1917</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6218</v>
+        <v>-3.948</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0376</v>
+        <v>-0.8702</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4158</v>
+        <v>-3.0777</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2042</v>
+        <v>-3.6064</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4227</v>
+        <v>-0.5968</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2185</v>
+        <v>-3.0096</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4176</v>
+        <v>-0.3416</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6149</v>
+        <v>-0.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3841</v>
+        <v>1.1207</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7652</v>
+        <v>0.8637</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3811</v>
+        <v>0.257</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6463</v>
+        <v>-1.0473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7333</v>
+        <v>1.1464</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3796</v>
+        <v>-2.1936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9331</v>
+        <v>0.9387</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0852</v>
+        <v>-0.0834</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0183</v>
+        <v>1.022</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3775</v>
+        <v>1.3672</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4444</v>
+        <v>-0.4285</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.015</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4174</v>
+        <v>0.0068</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1769</v>
+        <v>-0.0218</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1309</v>
+        <v>-1.7154</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6591</v>
+        <v>-1.2693</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4718</v>
+        <v>-0.4461</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7915</v>
+        <v>-0.793</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3117</v>
+        <v>-0.3103</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4798</v>
+        <v>-0.4828</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3297</v>
+        <v>0.3105</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1212</v>
+        <v>-1.1036</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5928</v>
+        <v>-0.1696</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9739</v>
+        <v>-0.5508</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3811</v>
+        <v>0.3812</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7757</v>
+        <v>-3.1588</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0005</v>
+        <v>-3.5025</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2249</v>
+        <v>0.3437</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8018</v>
+        <v>-2.8117</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5726</v>
+        <v>-2.587</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2292</v>
+        <v>-0.2247</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7633</v>
+        <v>-1.7951</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6113</v>
+        <v>-1.6385</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.0384</v>
+        <v>-1.0166</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7056</v>
+        <v>-0.0708</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>-0.2929</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1291</v>
+        <v>0.2221</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6227</v>
+        <v>-4.8421</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5332</v>
+        <v>-1.5666</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.0895</v>
+        <v>-3.2754</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.7548</v>
+        <v>-1.7549</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.3203</v>
+        <v>-1.3184</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4345</v>
+        <v>-0.4365</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2396</v>
+        <v>-0.2633</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5152</v>
+        <v>-1.4916</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4966</v>
+        <v>-1.48</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8127</v>
+        <v>0.5958</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1179</v>
+        <v>-0.1165</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9306</v>
+        <v>0.7123</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.6184</v>
+        <v>-5.0084</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1352</v>
+        <v>-2.8242</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4832</v>
+        <v>-2.1842</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.095</v>
+        <v>-3.1139</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.082</v>
+        <v>-2.0931</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.013</v>
+        <v>-1.0207</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7771</v>
+        <v>-1.8251</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0572</v>
+        <v>-1.0869</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7198</v>
+        <v>-0.7382</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3179</v>
+        <v>-1.2888</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0248</v>
+        <v>-1.0062</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1825</v>
+        <v>0.1877</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3907</v>
+        <v>0.6415</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.1664</v>
+        <v>-5.472599999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3558000000000012</v>
+        <v>0.7357000000000018</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.5221</v>
+        <v>-6.208</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.8636</v>
+        <v>-8.8964</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.4251</v>
+        <v>-5.4553</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4385</v>
+        <v>-3.441</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5208000000000008</v>
+        <v>0.2694000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>3.480300000000001</v>
+        <v>3.3119</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.9595</v>
+        <v>-3.0425</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.384400000000001</v>
+        <v>-9.166</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.905099999999999</v>
+        <v>-8.767200000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4792000000000001</v>
+        <v>-0.3986000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6098</v>
+        <v>-13.6577</v>
       </c>
       <c r="R14" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S14" t="n">
-        <v>6.200199999999997</v>
+        <v>6.9214</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8754</v>
+        <v>2.5981</v>
       </c>
       <c r="U14" t="n">
-        <v>4.3249</v>
+        <v>4.3237</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.503</v>
+        <v>-3.497600000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>11.5697</v>
+        <v>11.5258</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.0725</v>
+        <v>-15.0235</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2225</v>
+        <v>5.1089</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4737</v>
+        <v>3.7909</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7488</v>
+        <v>1.318</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0137</v>
+        <v>1.0307</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2152</v>
+        <v>-0.2045</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2289</v>
+        <v>1.2352</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4148</v>
+        <v>0.3995</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2282</v>
+        <v>0.2133</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5989</v>
+        <v>0.6311</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4434</v>
+        <v>-0.4179</v>
       </c>
       <c r="O15" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1618</v>
+        <v>-0.2797</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8166</v>
+        <v>-0.4626</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6548</v>
+        <v>0.1829</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W15" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.482</v>
+        <v>4.1423</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5287</v>
+        <v>4.8702</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0467</v>
+        <v>-0.7279</v>
       </c>
       <c r="G16" t="n">
-        <v>5.5694</v>
+        <v>5.5385</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5516</v>
+        <v>3.52</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0178</v>
+        <v>2.0185</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6851</v>
+        <v>5.6232</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1205</v>
+        <v>4.0669</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5646</v>
+        <v>1.5563</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1157</v>
+        <v>-0.0847</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5411</v>
+        <v>-0.8514</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1119</v>
+        <v>-0.4767</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.653</v>
+        <v>-0.3747</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>A. DOORNEKAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0454</v>
+        <v>2.0853</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3098</v>
+        <v>-0.5309</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7356</v>
+        <v>2.6162</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7533</v>
+        <v>1.363</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2526</v>
+        <v>1.2141</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.5007</v>
+        <v>0.1489</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9976</v>
+        <v>-0.0892</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4258</v>
+        <v>0.2241</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4234</v>
+        <v>-0.3132</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7557</v>
+        <v>1.4522</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6785</v>
+        <v>0.99</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0772</v>
+        <v>0.4622</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2524</v>
+        <v>-0.9394</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8953</v>
+        <v>-0.3719</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3572</v>
+        <v>-0.5675</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>-0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6575</v>
+        <v>1.9952</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1486</v>
+        <v>1.3712</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5088</v>
+        <v>0.6241</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5253</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9811</v>
+        <v>0.9876</v>
       </c>
       <c r="I18" t="n">
         <v>-0.4558</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2234</v>
+        <v>0.2156</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3019</v>
+        <v>0.3162</v>
       </c>
       <c r="N18" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2559</v>
+        <v>0.2593</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5483</v>
+        <v>-0.2195</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4869</v>
+        <v>-0.251</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DOORNEKAMP</t>
+          <t>P. MILLS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3632</v>
+        <v>1.3881</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7528</v>
+        <v>1.7867</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1161</v>
+        <v>-0.3987</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3481</v>
+        <v>0.1384</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1989</v>
+        <v>-0.9737</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1493</v>
+        <v>1.1121</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0788</v>
+        <v>0.5955</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2251</v>
+        <v>-0.1109</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3039</v>
+        <v>0.7064</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4269</v>
+        <v>-0.4571</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9737</v>
+        <v>-0.8628</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4532</v>
+        <v>0.4057</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6408</v>
+        <v>-0.6805</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6079</v>
+        <v>-0.6902</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0329</v>
+        <v>0.0097</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3856</v>
+        <v>1.2472</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>2.3367</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MILLS</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3064</v>
+        <v>0.8842</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4912</v>
+        <v>0.4648</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1848</v>
+        <v>0.4194</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1534</v>
+        <v>-1.743</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.974</v>
+        <v>-0.2446</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1274</v>
+        <v>-1.4985</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6422</v>
+        <v>-1.0134</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0906</v>
+        <v>0.4169</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7328</v>
+        <v>-1.4303</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4888</v>
+        <v>-0.7296</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8834</v>
+        <v>-0.6615</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3946</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7809</v>
+        <v>0.0825</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0434</v>
+        <v>0.0717</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2625</v>
+        <v>0.0108</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="W20" t="n">
-        <v>2.3461</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2205</v>
+        <v>0.4634</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4855</v>
+        <v>0.4567</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2651</v>
+        <v>0.0066</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1219</v>
+        <v>-0.1313</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7764</v>
+        <v>0.7701</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8983</v>
+        <v>-0.9014</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2079</v>
+        <v>-0.233</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7304</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="N21" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O21" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0186</v>
+        <v>-0.7711</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3992</v>
+        <v>-0.3997</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6194</v>
+        <v>-0.3714</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3601</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3793</v>
+        <v>0.1192</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.8042</v>
       </c>
       <c r="G22" t="n">
-        <v>1.0454</v>
+        <v>1.056</v>
       </c>
       <c r="H22" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.8871</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.4479</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.831</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.1353</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.3043</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.8997</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.4546</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.4451</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-0.8542999999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-1.1503</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.2959</v>
-      </c>
       <c r="P22" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0445</v>
+        <v>-0.3752</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0735</v>
+        <v>-0.0218</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7422</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4009</v>
+        <v>-0.4023</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3414</v>
+        <v>-0.3069</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0131</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1703</v>
+        <v>-0.1668</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5024</v>
+        <v>-0.4727</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2937</v>
+        <v>-0.2636</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1041</v>
+        <v>-0.8192</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7025</v>
+        <v>0.9335</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8066</v>
+        <v>-1.7527</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4464</v>
+        <v>1.4545</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2495</v>
+        <v>0.2553</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1968</v>
+        <v>1.1992</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4858</v>
+        <v>1.4818</v>
       </c>
       <c r="K24" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1568</v>
+        <v>1.1543</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0395</v>
+        <v>-0.0273</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O24" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8169</v>
+        <v>-0.5517</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5565</v>
+        <v>-0.3207</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2604</v>
+        <v>-0.2309</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.7838</v>
+        <v>-3.5113</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7772</v>
+        <v>-1.5586</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0066</v>
+        <v>-1.9527</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6636</v>
+        <v>-0.6627</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.5223</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1413</v>
+        <v>-0.14</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2795</v>
+        <v>0.2673</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1283</v>
+        <v>-0.1346</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9431</v>
+        <v>-0.93</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7988</v>
+        <v>-0.5331</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6956</v>
+        <v>-0.4601</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="26">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.1409</v>
+        <v>-4.1733</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.6127</v>
+        <v>-5.6381</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4718</v>
+        <v>1.4649</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3138</v>
+        <v>0.3293</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4977</v>
+        <v>0.5078</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1839</v>
+        <v>-0.1785</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0036</v>
+        <v>-0.0029</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3102</v>
+        <v>0.3322</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.2172</v>
+        <v>-5.2355</v>
       </c>
       <c r="R26" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5985</v>
+        <v>-0.6328</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.3992</v>
+        <v>-0.3997</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1993</v>
+        <v>-0.2331</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>6.166399999999998</v>
+        <v>6.1694</v>
       </c>
       <c r="E27" t="n">
-        <v>5.9757</v>
+        <v>5.663299999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1904999999999997</v>
+        <v>0.5061</v>
       </c>
       <c r="G27" t="n">
-        <v>8.863600000000002</v>
+        <v>8.896400000000002</v>
       </c>
       <c r="H27" t="n">
-        <v>5.4251</v>
+        <v>5.4552</v>
       </c>
       <c r="I27" t="n">
-        <v>3.438499999999999</v>
+        <v>3.441000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>9.384400000000001</v>
+        <v>9.166</v>
       </c>
       <c r="K27" t="n">
-        <v>8.905100000000001</v>
+        <v>8.7674</v>
       </c>
       <c r="L27" t="n">
-        <v>0.4792999999999998</v>
+        <v>0.3986000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5209000000000001</v>
+        <v>-0.2695000000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>-3.4804</v>
+        <v>-3.3123</v>
       </c>
       <c r="O27" t="n">
-        <v>2.9594</v>
+        <v>3.042600000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0.0001000000000006551</v>
       </c>
       <c r="Q27" t="n">
-        <v>-13.6099</v>
+        <v>-13.6577</v>
       </c>
       <c r="R27" t="n">
-        <v>13.6101</v>
+        <v>13.6581</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.200199999999999</v>
+        <v>-6.224600000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.3247</v>
+        <v>-4.323399999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8752</v>
+        <v>-1.901</v>
       </c>
       <c r="V27" t="n">
-        <v>3.503000000000001</v>
+        <v>3.4976</v>
       </c>
       <c r="W27" t="n">
-        <v>14.5262</v>
+        <v>14.4788</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.0233</v>
+        <v>-10.9811</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104701_W27.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104701_W27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-15.0235</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104701_W27.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-10.9811</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
